--- a/test-cases/test-summary.xlsx
+++ b/test-cases/test-summary.xlsx
@@ -443,7 +443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HW06 API Testing — Test Summary</t>
+          <t>HW06 API Testing - Tổng hợp test case</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Suite chạy xanh — assertion của case known-bug kiểm hành vi quan sát (được gắn nhãn [BUG-*]); lỗi được đếm riêng ở cột Bugs.</t>
+          <t>Suite chạy xanh — assertion của case bug đã biết kiểm hành vi quan sát (được gắn nhãn [BUG-*]); lỗi được đếm riêng ở cột Bug.</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>AI-generated</t>
+          <t>AI sinh</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -518,22 +518,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Newman assertions</t>
+          <t>Số assertion Newman</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Đạt</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Không đạt</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Bugs</t>
+          <t>Bug</t>
         </is>
       </c>
     </row>
@@ -547,10 +547,10 @@
         <v>40</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" t="n">
         <v>45</v>
@@ -624,17 +624,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Tổng</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
         <v>115</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>233</v>

--- a/test-cases/test-summary.xlsx
+++ b/test-cases/test-summary.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Test Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TC-FR01-Register" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TC-FR08-Checkout" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="TC-FR14-Category" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,13 +30,18 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="13"/>
+      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font/>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -42,11 +50,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -54,14 +87,64 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,12 +514,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -448,208 +531,7490 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Sinh viên:</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Hà Bảo Ngọc — 23127300</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Nhóm:</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>N08 — CS423/CSC15003</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Ngày:</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Ghi chú:</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Suite chạy xanh — assertion của case bug đã biết kiểm hành vi quan sát (được gắn nhãn [BUG-*]); lỗi được đếm riêng ở cột Bug.</t>
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>AI sinh</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Sinh viên bổ sung</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Tổng thiết kế</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Số assertion Newman</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Đạt</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Không đạt</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Bug</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>FR-01 Register</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="6" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>FR-08 Checkout</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="6" t="n">
         <v>76</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="6" t="n">
         <v>76</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="6" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>FR-14 Category</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="6" t="n">
         <v>112</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="6" t="n">
         <v>112</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="6" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Tổng</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="8" t="n">
         <v>115</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="8" t="n">
         <v>132</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="8" t="n">
         <v>233</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="8" t="n">
         <v>233</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="8" t="n">
         <v>10</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B5:H5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FR-01 Register — Ma trận test case chi tiết (AI sinh + audit + bổ sung)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Nguồn</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Nhóm kiểm thử / Mô tả</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Dữ liệu / Hành động</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Tiền điều kiện</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Kết quả mong đợi (theo spec)</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Lý do audit / Vì sao AI bỏ sót</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Điều chỉnh / Hành vi quan sát</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Bug liên quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-001</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Đăng ký hợp lệ</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>"Nguyen Van A" / "valid@hw06.test" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>200 OK; `{message:"User registered successfully", id:&lt;int&gt;}`</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 200; khớp schema</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-002</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Tên rỗng</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>"" / "email@hw06.test" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; lỗi validation</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-003</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Thiếu trường tên</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>(omitted) / "email@hw06.test" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; lỗi validation</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-004</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Tên chỉ gồm khoảng trắng</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>"   " / "email@hw06.test" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; từ chối khoảng trắng</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-005</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Tên quá dài</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>"A" * 300 / "email@hw06.test" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; giới hạn độ dài</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-006</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Tên có Unicode</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>"Nguyễn Văn Á" / "email@hw06.test" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>200 OK (nếu hỗ trợ) hoặc 400</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Chấp nhận hoặc từ chối Unicode một cách nhất quán</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-007</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Tên chỉ gồm chữ số</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>"12345" / "email@hw06.test" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>200 OK (nếu cho phép chuỗi số) hoặc 400</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Chấp nhận hoặc từ chối theo spec</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-008</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Tên có ký tự đặc biệt</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>"John@O'Brien#" / "email@hw06.test" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>200 OK hoặc 400</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Chấp nhận hoặc từ chối ký tự đặc biệt</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-009</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Email hợp lệ</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "valid.email@domain.com" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 200</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-010</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Email rỗng</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; validation</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-011</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Thiếu trường email</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / (omitted) / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; validation</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-012</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Email thiếu ký tự @</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "invalidemail.com" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; định dạng email</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-013</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Email thiếu domain</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "user@" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; email thiếu thành phần</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-014</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Email thiếu TLD</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "user@domain" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request hoặc 200 (tùy validation)</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Kiểm tra độ nghiêm ngặt của định dạng email</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-015</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Email có khoảng trắng đầu chuỗi</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / " user@hw06.test" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; khoảng trắng</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-016</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Email có khoảng trắng cuối chuỗi</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "user@hw06.test " / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request hoặc được trim</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Kiểm tra hành vi trim</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-017</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Email chứa SQL meta OR</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "a' OR '1'='1" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; chống SQL injection</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400; không bị injection</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-018</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Email chứa SQL meta UNION</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "a' UNION SELECT" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; chống SQL injection</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400; không bị injection</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-019</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Email chứa XSS script tag</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "&lt;script&gt;alert('xss')&lt;/script&gt;" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; chống XSS</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400; không có XSS</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-020</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Email chứa XSS event</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "test@hw06.test' onclick='alert(1)'" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; chống XSS</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-021</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Email dài 320 ký tự</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "a" * 300 + "@test.com" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; giới hạn độ dài</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-022</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Email trùng theo đặc tả</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>"User A" / "dup@hw06.test" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản với email `dup@hw06.test` đã tồn tại</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Theo spec: phải từ chối với 400 hoặc 409</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Kiểm tra enforce tính duy nhất</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>AI đưa ra giả định quá lạc quan về validation, security hoặc business rule của SUT.</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>Điều chỉnh expected theo hành vi quan sát được và gắn known bug khi cần.</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR01-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-023</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Mật khẩu hợp lệ</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "email@hw06.test" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 200</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-024</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Mật khẩu rỗng</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "email@hw06.test" / ""</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; validation</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR01-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-025</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Thiếu trường mật khẩu</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "email@hw06.test" / (omitted)</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; validation</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-026</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Mật khẩu quá ngắn (3 ký tự)</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "email@hw06.test" / "abc"</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; độ dài tối thiểu 8</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR01-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-027</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Mật khẩu quá ngắn (7 ký tự)</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "email@hw06.test" / "Pass12!"</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; độ dài tối thiểu 8</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR01-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-028</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Mật khẩu thiếu chữ hoa</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "email@hw06.test" / "password123!"</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; độ phức tạp</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400 hoặc 200 (kiểm tra theo spec)</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR01-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-029</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Mật khẩu thiếu chữ số</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "email@hw06.test" / "Password!"</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; độ phức tạp</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400 hoặc 200</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR01-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-030</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Mật khẩu thiếu ký tự đặc biệt</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "email@hw06.test" / "Password123"</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; độ phức tạp</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400 hoặc 200</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR01-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-031</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Mật khẩu chỉ gồm khoảng trắng</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "email@hw06.test" / "        "</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; khoảng trắng</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR01-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-032</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Mật khẩu quá dài (500 ký tự)</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "email@hw06.test" / "Pass" * 125</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; giới hạn độ dài</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K34" s="10" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-033</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Schema - Body rỗng</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>(body JSON rỗng `{}`)</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; thiếu field</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-034</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Schema - Có field thừa</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>"Test" / "email@hw06.test" / "Password123!" + {"extra":"field"}</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>200 OK (bỏ qua field thừa) hoặc 400</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Kiểm tra schema nghiêm ngặt</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K36" s="10" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-035</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Trạng thái - Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>"Alice" / "alice@hw06.test" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có tài khoản trước đó</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>200 OK; id được sinh</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 200; id là số nguyên</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-036</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Trạng thái - Email trùng (bug đã biết)</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>"Bob" / "bob@hw06.test" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>`bob@hw06.test` đã tồn tại</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>**Phải từ chối (400)** nhưng **SUT chèn dòng thứ hai và trả 200**</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi **200** (BUG)</t>
+        </is>
+      </c>
+      <c r="H38" s="13" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>AI đưa ra giả định quá lạc quan về validation, security hoặc business rule của SUT.</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>Điều chỉnh expected theo hành vi quan sát được và gắn known bug khi cần.</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR01-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-037</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Bảo mật - Lộ mật khẩu plaintext</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>"Charlie" / "charlie@hw06.test" / "SecurePass123!"</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>Sau khi đăng ký qua /login</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>Password không được xuất hiện trong `/api/users/me`</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>Kiểm tra response `/api/users/me`</t>
+        </is>
+      </c>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>AI đưa ra giả định quá lạc quan về validation, security hoặc business rule của SUT.</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>Điều chỉnh expected theo hành vi quan sát được và gắn known bug khi cần.</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR01-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-038</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Bảo mật - Đăng ký hàng loạt</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Cùng email base, biến thể +1/+2, gửi nhanh 100 lần</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>Không có auth/rate limit</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>200 OK nhưng tạo tải lớn lên server</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>Quan sát hệ thống có áp dụng rate-limit không</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K40" s="10" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-039</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Bảo mật - SQL injection trong name</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>"'; DROP TABLE users; --" / "email@hw06.test" / "Password123!"</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request; không bị injection</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>Xác minh bảng vẫn tồn tại sau test</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K41" s="10" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR01-040</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Bảo mật - SQL injection trong password</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>"Test User" / "email@hw06.test" / "Pass' OR '1'='1"</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>Tài khoản mới</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request hoặc 200 (parameterized)</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>Kiểm tra dữ liệu được lưu an toàn</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>TC-EX-001</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>SV bổ sung</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Email trùng được chấp nhận (không có unique constraint)</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Đăng ký `Alice / alice@hw06.test / Password123!`, sau đó đăng ký `Bob / alice@hw06.test / Password123!`.</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr"/>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>Theo spec phải trả 400/409; hành vi quan sát được là 200 và chèn dòng thứ hai.</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr"/>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>AI giả định hành vi RDBMS phổ biến là email có unique constraint. SUT thực tế không enforce tính duy nhất.</t>
+        </is>
+      </c>
+      <c r="J43" s="10" t="inlineStr"/>
+      <c r="K43" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR01-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>TC-EX-002</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>SV bổ sung</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>Body rỗng được chấp nhận</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Gửi `POST /api/register` với body `{}`.</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr"/>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>Phải trả 400 Bad Request; nếu SUT trả 200 thì đây là lỗi validation nghiêm trọng.</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr"/>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>AI chưa nhấn mạnh case `{}` dù spec yêu cầu đủ name/email/password.</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="inlineStr"/>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR01-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>TC-EX-003</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>SV bổ sung</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>Lộ plaintext password qua `/api/users/me`</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Đăng ký Charlie, login lấy JWT, gọi `GET /api/users/me`.</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr"/>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>Response user không được chứa `password`.</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr"/>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>AI tập trung vào register endpoint và bỏ sót endpoint sau đăng nhập.</t>
+        </is>
+      </c>
+      <c r="J45" s="10" t="inlineStr"/>
+      <c r="K45" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR01-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>TC-EX-004</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>SV bổ sung</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Mật khẩu yếu được chấp nhận</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Đăng ký David với password `123`.</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr"/>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>Phải trả 400 Bad Request; nếu 200 thì thiếu enforce password complexity.</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr"/>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>AI chưa tách rõ case mật khẩu cực yếu như `123`.</t>
+        </is>
+      </c>
+      <c r="J46" s="10" t="inlineStr"/>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR01-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>TC-EX-005</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>SV bổ sung</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>Email chỉ gồm khoảng trắng được chấp nhận</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>Đăng ký Eve với email gồm bốn khoảng trắng.</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr"/>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>Phải trả 400 Bad Request; nếu 200 thì thiếu validate email format/trim.</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr"/>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>AI có kiểm tra leading/trailing space nhưng thiếu pure whitespace.</t>
+        </is>
+      </c>
+      <c r="J47" s="10" t="inlineStr"/>
+      <c r="K47" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR01-002</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FR-08 Checkout — Ma trận test case chi tiết (AI sinh + audit + bổ sung)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Nguồn</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Nhóm kiểm thử / Mô tả</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Dữ liệu / Hành động</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Tiền điều kiện</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Kết quả mong đợi (theo spec)</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Lý do audit / Vì sao AI bỏ sót</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Điều chỉnh / Hành vi quan sát</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Bug liên quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-001</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Thanh toán hợp lệ</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>200000 / "123 Le Loi, Q1, TP.HCM" / user</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>200 OK; `{message:"Checkout successful", orderId:&lt;int&gt;}`</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 200; khớp schema; orderId is integer</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-002</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Xác thực - Không có token</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>200000 / "123 Le Loi, Q1" / none</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Không có Authorization header</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 401</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-003</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Xác thực - Token không hợp lệ</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>200000 / "123 Le Loi, Q1" / invalid</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Token sai định dạng "Bearer not.a.real.token"</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>403 Forbidden</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 403</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-004</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Xác thực - User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>150000 / "456 Nguyen Hue, Q3" / user</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 200; orderId returned</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-005</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>total_amount bằng 0</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>0 / "123 Le Loi, Q1" / user</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request (should reject)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>AI đưa ra giả định quá lạc quan về validation, security hoặc business rule của SUT.</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Điều chỉnh expected theo hành vi quan sát được và gắn known bug khi cần.</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR08-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-006</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>total_amount âm</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>-5000 / "123 Le Loi, Q1" / user</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request (should reject)</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>AI đưa ra giả định quá lạc quan về validation, security hoặc business rule của SUT.</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Điều chỉnh expected theo hành vi quan sát được và gắn known bug khi cần.</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR08-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-007</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>total_amount dương nhỏ</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>1 / "123 Le Loi, Q1" / user</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>200 OK (boundary)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 200</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-008</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>total_amount dương lớn</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>999999999 / "123 Le Loi, Q1" / user</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 200</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-009</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>total_amount kiểu float</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>199.99 / "123 Le Loi, Q1" / user</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>200 OK (accepted) or 400</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Check if float handled correctly</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-010</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Thiếu total_amount</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>(omitted) / "123 Le Loi, Q1" / user</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-011</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>total_amount là chuỗi không phải số</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>"abc" / "123 Le Loi, Q1" / user</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-012</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>total_amount là chuỗi rỗng</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>"" / "123 Le Loi, Q1" / user</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-013</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>shipping_address hợp lệ</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>200000 / "789 Tran Hung Dao, Q5, TP.HCM" / user</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 200</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-014</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>shipping_address rỗng</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>200000 / "" / user</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request (should reject)</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>AI đưa ra giả định quá lạc quan về validation, security hoặc business rule của SUT.</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>Điều chỉnh expected theo hành vi quan sát được và gắn known bug khi cần.</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-015</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Thiếu shipping_address</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>200000 / (omitted) / user</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-016</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>shipping_address quá dài</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>200000 / ("A" * 500) / user</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request (giới hạn độ dài)</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-017</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>shipping_address có Unicode</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>200000 / "123 Lê Lợi, Quận 1, Thành phố Hồ Chí Minh" / user</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>200 OK (unicode supported)</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 200</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-018</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>shipping_address chỉ gồm khoảng trắng</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>200000 / "   " / user</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-019</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Schema - Body rỗng</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>{} / user</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-020</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Schema - Có field thừa</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>200000 / "123 Le Loi" / user + {"extra":"field"}</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>200 OK (bỏ qua field thừa) hoặc 400</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Kiểm tra schema nghiêm ngặt</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-021</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Nghiệp vụ - Kiểm tra giỏ hàng</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>50000 / "123 Le Loi" / user</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>Cart total is 200000 (mismatch)</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request (should validate)</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>AI đưa ra giả định quá lạc quan về validation, security hoặc business rule của SUT.</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>Điều chỉnh expected theo hành vi quan sát được và gắn known bug khi cần.</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-022</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Trạng thái - Đơn hàng được tạo</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>200000 / "123 Le Loi" / user</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Checkout hợp lệ</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Đơn hàng tồn tại with status "pending"</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Query DB hoặc GET /api/orders/:id xác nhận status pending</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-023</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Trạng thái - pending sang confirmed</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Admin cập nhật `orderId` sang status "confirmed"</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>Đơn hàng đang ở trạng thái pending</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>200 OK; status updated</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>PUT /api/admin/orders/:id/status trả 200</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-024</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Trạng thái - confirmed sang shipping</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Admin cập nhật `orderId` sang status "shipping"</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Đơn hàng đang ở trạng thái confirmed</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>200 OK; status updated</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>PUT /api/admin/orders/:id/status trả 200</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-025</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Trạng thái - shipping sang delivered</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Admin cập nhật `orderId` sang status "delivered"</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Đơn hàng đang ở trạng thái shipping</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>200 OK; status updated</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>PUT /api/admin/orders/:id/status trả 200</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-026</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Trạng thái - pending sang delivered không hợp lệ</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Admin cập nhật `orderId` sang status "delivered"</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Đơn hàng đang ở trạng thái pending</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request (illegal jump)</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-027</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Trạng thái - pending sang shipping không hợp lệ</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Admin cập nhật `orderId` sang status "shipping"</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>Đơn hàng đang ở trạng thái pending</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request (phải confirmed trước)</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-028</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Trạng thái - pending sang canceled hợp lệ</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Admin cập nhật `orderId` sang status "canceled"</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Đơn hàng đang ở trạng thái pending</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 200</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-029</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Trạng thái - canceled sang delivered không hợp lệ</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Admin cập nhật `orderId` sang status "delivered"</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>Đơn hàng đang ở trạng thái canceled</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request (canceled là trạng thái kết thúc)</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>AI đưa ra giả định quá lạc quan về validation, security hoặc business rule của SUT.</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>Điều chỉnh expected theo hành vi quan sát được và gắn known bug khi cần.</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR08-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-030</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Bảo mật - IDOR đọc đơn hàng</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>GET /api/orders/:id with no token</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Đơn hàng tồn tại</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>401 Unauthorized (phải yêu cầu xác thực)</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 401</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>AI đưa ra giả định quá lạc quan về validation, security hoặc business rule của SUT.</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>Điều chỉnh expected theo hành vi quan sát được và gắn known bug khi cần.</t>
+        </is>
+      </c>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR08-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-031</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Bảo mật - IDOR đọc đơn hàng user khác</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>GET /api/orders/:id with userB token</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>Đơn hàng thuộc userA</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>403 Forbidden (phải từ chối quyền truy cập)</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 403</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>AI đưa ra giả định quá lạc quan về validation, security hoặc business rule của SUT.</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>Điều chỉnh expected theo hành vi quan sát được và gắn known bug khi cần.</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR08-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-032</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>SQL injection trong shipping_address</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>200000 / "123' OR '1'='1" / user</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>200 OK (parameterized) or 400</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>Check if safely stored</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K34" s="10" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-033</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>XSS trong shipping_address</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>200000 / "&lt;script&gt;alert('xss')&lt;/script&gt;" / user</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>400 Bad Request or sanitized</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 400 or stored safely</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-034</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Biên - total_amount = 1</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>1 / "123 Le Loi" / user</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 200</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K36" s="10" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-035</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Biên - total_amount = MAX_INT</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>2147483647 / "123 Le Loi" / user</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>200 OK</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>Mã phản hồi 200</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-EXT-001</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>SV bổ sung</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Bảo mật - IDOR đọc order không cần auth</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>`GET /api/orders/{{lastOrderId}}` không có Authorization header</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>Đơn hàng tồn tại từ checkout trước</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>Quan sát được 200 OK; đúng ra phải là 401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr"/>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>AI giả định endpoint đã enforce auth nhưng SUT không enforce.</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="inlineStr"/>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR08-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-EXT-002</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>SV bổ sung</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Nghiệp vụ - `total_amount` âm</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>`POST /api/checkout` với `total_amount=-10000`</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>Quan sát được 200 OK; đúng ra phải là 400 Bad Request</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr"/>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>AI giả định backend validate số tiền dương.</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="inlineStr"/>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR08-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-EXT-003</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>SV bổ sung</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>State machine - `canceled→delivered` không hợp lệ</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>`PUT /api/admin/orders/:id/status` với `{ "status": "delivered" }`</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>Order đang ở trạng thái `canceled`</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>Quan sát được 200 OK; đúng ra phải là 400 Bad Request</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr"/>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>AI liệt kê transition này là illegal nhưng cần case runtime để bắt bug.</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="inlineStr"/>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR08-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-EXT-004</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>SV bổ sung</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Nghiệp vụ - checkout khi giỏ hàng rỗng</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Checkout với user token, total_amount/address hợp lệ nhưng cart rỗng</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>Giỏ hàng chưa có item</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>Đúng ra phải trả 400; nếu 200 thì tạo order rỗng</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr"/>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>AI không kiểm tra quan hệ giữa cart state và checkout.</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="inlineStr"/>
+      <c r="K41" s="10" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR08-EXT-005</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>SV bổ sung</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Type coercion - `total_amount` dạng chuỗi số</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>`total_amount="50000"` thay vì number</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>User token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>Strict schema nên reject 400 hoặc ghi nhận coercion</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr"/>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>AI test chuỗi không phải số nhưng bỏ sót chuỗi số có thể bị JS ép kiểu.</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="inlineStr"/>
+      <c r="K42" s="10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FR-14 Category CRUD — Ma trận test case chi tiết (AI sinh + audit + bổ sung)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Nguồn</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Nhóm kiểm thử / Mô tả</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Dữ liệu / Hành động</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Tiền điều kiện</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Kết quả mong đợi (theo spec)</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Lý do audit / Vì sao AI bỏ sót</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Điều chỉnh / Hành vi quan sát</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Bug liên quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-001</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>POST tên hợp lệ</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"Điện thoại"}`</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>200, `{message, id}`</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Theo spec §3.4</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-002</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>POST tên hợp lệ</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"Laptop"}`</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>200, `{message, id}`</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Theo spec §3.4</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-003</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>POST tên rỗng</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":""}`</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>400, lỗi validation</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Ràng buộc input</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR14-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-004</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>POST thiếu tên</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>`{}`</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>400, missing field</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Ràng buộc input</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-005</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>POST tên chỉ gồm khoảng trắng</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"   "}`</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>400, invalid format</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Ràng buộc input</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR14-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-006</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>POST tên quá dài</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"A" * 256}`</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>400 or truncated</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Length limit</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-007</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>POST tên Unicode</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"Đồng hồ thông minh"}`</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>200, `{message, id}`</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Hỗ trợ Unicode</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-008</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>POST tên có ký tự đặc biệt</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"Phụ kiện &amp; Linh kiện"}`</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>200, `{message, id}`</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Ký tự đặc biệt</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-009</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>POST tên dạng số</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"12345"}`</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>200, `{message, id}`</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Cho phép chuỗi số</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-010</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>POST tên trùng</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"Điện thoại"}`</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Exists, admin token</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>400 or accepts</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Tính duy nhất</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>AI đưa ra giả định quá lạc quan về validation, security hoặc business rule của SUT.</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>Điều chỉnh expected theo hành vi quan sát được và gắn known bug khi cần.</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR14-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-011</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>POST tên chứa SQL meta</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"'; DROP TABLE categories;--"}`</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>200, escaped</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>SQL injection</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-012</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>POST tên chứa XSS</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"&lt;script&gt;alert('xss')&lt;/script&gt;"}`</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>200, escaped</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>XSS</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-013</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>POST tên chứa null byte</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"Test\u0000"}`</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>400 or sanitized</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Null byte</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-014</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>POST không có token</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"Test"}`</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>Không có Authorization header</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Yêu cầu xác thực</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-015</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>POST token không hợp lệ</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"Test"}`</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>`Bearer invalid.token`</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>403 Forbidden</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Kiểm tra token</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-016</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>POST bằng user token</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"Test"}`</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Valid user (non-admin) token</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>403 Forbidden</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Yêu cầu role admin</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>AI đưa ra giả định quá lạc quan về validation, security hoặc business rule của SUT.</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>Điều chỉnh expected theo hành vi quan sát được và gắn known bug khi cần.</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR14-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-017</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>POST bằng admin token</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"Valid"}`</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Admin token hợp lệ</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>200, `{message, id}`</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Quyền admin</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-018</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>POST có field thừa</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"Test","extra":"field"}`</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>200, extra ignored</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Robustness</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-019</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>POST sai kiểu dữ liệu</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":123}`</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>400, type error</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>Type validation</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-020</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>GET danh sách tất cả</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>DB có category</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>200, array object</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Theo spec §3.4</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-021</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>GET danh sách rỗng</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>DB rỗng</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>200, `[]`</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>Tập rỗng</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-022</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>GET không cần xác thực</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Không có token</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>200, public endpoint</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Public read</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-023</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>PUT đổi tên hợp lệ</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"New Name"}`</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>Id hợp lệ, admin token</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>200, `{message}`</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>Theo spec §3.4</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-024</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>PUT tên rỗng</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":""}`</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Id hợp lệ, admin token</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>400, validation</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Ràng buộc input</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-025</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>PUT thiếu tên</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>`{}`</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Id hợp lệ, admin token</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>400, missing field</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>Ràng buộc input</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-026</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>PUT id không tồn tại</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"Test"}`</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>id=999999, admin token</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>404 Not Found</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Kiểm tra resource</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>AI đưa ra giả định quá lạc quan về validation, security hoặc business rule của SUT.</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>Điều chỉnh expected theo hành vi quan sát được và gắn known bug khi cần.</t>
+        </is>
+      </c>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR14-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-027</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>PUT không có token</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"Test"}`</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>Id hợp lệ, no token</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>Yêu cầu xác thực</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-028</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>PUT bằng user token</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"Test"}`</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Id hợp lệ, user token</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>403 Forbidden</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Yêu cầu role admin</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>AI đưa ra giả định quá lạc quan về validation, security hoặc business rule của SUT.</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>Điều chỉnh expected theo hành vi quan sát được và gắn known bug khi cần.</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR14-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-029</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>PUT tên chứa SQL injection</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"' OR '1'='1"}`</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>Id hợp lệ, admin token</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>200, escaped</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>SQL injection</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-030</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>DELETE id hợp lệ</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Id hợp lệ, admin token</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>200, `{message}`</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Theo spec §3.4</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-031</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>DELETE id không tồn tại</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>id=999999, admin token</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>404 Not Found</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>Kiểm tra resource</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>AI đưa ra giả định quá lạc quan về validation, security hoặc business rule của SUT.</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>Điều chỉnh expected theo hành vi quan sát được và gắn known bug khi cần.</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR14-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-032</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>DELETE không có token</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Id hợp lệ, no token</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>Yêu cầu xác thực</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K34" s="10" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-033</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>DELETE bằng user token</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>Id hợp lệ, user token</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>403 Forbidden</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>Yêu cầu role admin</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>INVALID</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>AI đưa ra giả định quá lạc quan về validation, security hoặc business rule của SUT.</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>Điều chỉnh expected theo hành vi quan sát được và gắn known bug khi cần.</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR14-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-034</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Lifecycle tạo-đọc-cập nhật-xóa</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Chuỗi thao tác đầy đủ</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>All 200, state reflects</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Luồng trạng thái</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K36" s="10" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-035</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>GET sau khi tạo</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>POST rồi GET</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>Admin token cho POST</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>GET list có category mới</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>Tính nhất quán</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-036</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>GET sau khi cập nhật</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>PUT rồi GET</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>GET phản ánh tên đã cập nhật</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>Tính nhất quán</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-037</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>GET sau khi xóa</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>DELETE rồi GET</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>GET list không còn category đã xóa</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>Tính nhất quán</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-038</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>POST biên độ dài 255</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"A" * 255}`</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>200 or 400</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>Biên độ dài</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Oracle phù hợp đặc tả và có thể thực thi trực tiếp.</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>Không cần điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="K40" s="10" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-039</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>POST tên có khoảng trắng đầu chuỗi</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":" Leading"}`</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>200 or trimmed</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>Xử lý khoảng trắng</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K41" s="10" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-040</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>AI sinh</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>POST tên có khoảng trắng cuối chuỗi</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>`{"name":"Trailing "}`</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>Admin token</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>200 or trimmed</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>Xử lý khoảng trắng</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>Spec hoặc error contract chưa đủ rõ, cần chạy và ghi nhận hành vi thực tế của SUT.</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>Giữ case ở chế độ quan sát hoặc nới oracle theo nhóm status hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-041</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>SV bổ sung</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>User thường tạo category (role escalation)</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>`POST /api/categories` với user token</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr"/>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>Phải trả 403 Forbidden</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>Quan sát được 200 OK</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr"/>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>Quan sát được 200 OK</t>
+        </is>
+      </c>
+      <c r="K43" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR14-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-042</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>SV bổ sung</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>User thường xóa category (role escalation)</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>`DELETE /api/categories/:id` với user token</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr"/>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>Phải trả 403 Forbidden</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>Quan sát được 200 OK</t>
+        </is>
+      </c>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr"/>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>Quan sát được 200 OK</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR14-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-043</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>SV bổ sung</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>PUT id không tồn tại vẫn thành công</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>`PUT /api/categories/999999`</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr"/>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>Phải trả 404 Not Found</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>Quan sát được 200 OK</t>
+        </is>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="I45" s="10" t="inlineStr"/>
+      <c r="J45" s="10" t="inlineStr">
+        <is>
+          <t>Quan sát được 200 OK</t>
+        </is>
+      </c>
+      <c r="K45" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR14-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-044</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>SV bổ sung</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>DELETE id không tồn tại vẫn thành công</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>`DELETE /api/categories/999999`</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr"/>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>Phải trả 404 Not Found</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>Quan sát được 200 OK</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="I46" s="10" t="inlineStr"/>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>Quan sát được 200 OK</t>
+        </is>
+      </c>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR14-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-045</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>SV bổ sung</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>Tên category trùng được chấp nhận</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>POST category `Điện thoại` hai lần</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr"/>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>Phải trả 400/409</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>Quan sát được 200 OK cả hai lần</t>
+        </is>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="I47" s="10" t="inlineStr"/>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>Quan sát được 200 OK cả hai lần</t>
+        </is>
+      </c>
+      <c r="K47" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR14-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-046</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>SV bổ sung</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Tên category rỗng được chấp nhận</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>`POST /api/categories` với `{ "name": "" }`</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr"/>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>Phải trả 400 Bad Request</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>Quan sát được 200 OK</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr"/>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>Quan sát được 200 OK</t>
+        </is>
+      </c>
+      <c r="K48" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR14-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>TC-FR14-047</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>SV bổ sung</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>Tên category chỉ gồm khoảng trắng được chấp nhận</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>`POST /api/categories` với `{ "name": "   " }`</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr"/>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>Phải trả 400 Bad Request</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>Quan sát được 200 OK</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>EXTENDED</t>
+        </is>
+      </c>
+      <c r="I49" s="10" t="inlineStr"/>
+      <c r="J49" s="10" t="inlineStr">
+        <is>
+          <t>Quan sát được 200 OK</t>
+        </is>
+      </c>
+      <c r="K49" s="10" t="inlineStr">
+        <is>
+          <t>BUG-FR14-004</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>